--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B2" t="n">
-        <v>91184</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R2" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,7 +775,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,50 +809,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R3" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125607506</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,12 +791,7 @@
         <v>125607274</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R2" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B3" t="n">
-        <v>91238</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,45 +795,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R3" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B2" t="n">
-        <v>91245</v>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R2" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>91246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,50 +799,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R3" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>91246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R2" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B3" t="n">
-        <v>91246</v>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,45 +795,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R3" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125607274</v>
       </c>
       <c r="B2" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B2" t="n">
-        <v>91250</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R2" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>91252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,50 +799,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R3" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -791,7 +791,7 @@
         <v>125607274</v>
       </c>
       <c r="B3" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>91256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R2" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,45 +795,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R3" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,7 +879,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42390-2020 artfynd.xlsx
+++ b/artfynd/A 42390-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607274</v>
+        <v>125607506</v>
       </c>
       <c r="B2" t="n">
-        <v>91256</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800938</v>
+        <v>800936</v>
       </c>
       <c r="R2" t="n">
-        <v>7284424</v>
+        <v>7284481</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -765,7 +770,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607506</v>
+        <v>125607274</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>91256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,50 +799,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvavisträsket, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800936</v>
+        <v>800938</v>
       </c>
       <c r="R3" t="n">
-        <v>7284481</v>
+        <v>7284424</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
